--- a/output/StructureDefinition-Device-HiMi.xlsx
+++ b/output/StructureDefinition-Device-HiMi.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-19T17:49:48+02:00</t>
+    <t>2025-08-20T09:32:40+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-Device-HiMi.xlsx
+++ b/output/StructureDefinition-Device-HiMi.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-20T09:32:40+02:00</t>
+    <t>2025-08-21T10:18:14+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -4523,7 +4523,7 @@
         <v>78</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>16</v>
+        <v>79</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>16</v>
@@ -5506,13 +5506,13 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>16</v>
+        <v>79</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>16</v>

--- a/output/StructureDefinition-Device-HiMi.xlsx
+++ b/output/StructureDefinition-Device-HiMi.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-21T10:18:14+02:00</t>
+    <t>2025-08-21T11:34:25+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-Device-HiMi.xlsx
+++ b/output/StructureDefinition-Device-HiMi.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-21T11:34:25+02:00</t>
+    <t>2025-08-21T15:49:15+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
